--- a/Ideologies List.xlsx
+++ b/Ideologies List.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emb29\Documents\Paradox Interactive\Hearts of Iron IV\mod\Legacy-of-Kattail\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91C3DCFD-C09E-4E3F-AAEC-C25364E57E72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{32563DAA-5572-4538-B691-45CB5ED6F138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{E4DD147F-DB29-4F8A-B6A9-D2DAD2D36CC1}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="103">
   <si>
     <t>Social Democratic</t>
   </si>
@@ -53,9 +54,6 @@
     <t>Social Conservative</t>
   </si>
   <si>
-    <t>Authoritarian Democrat</t>
-  </si>
-  <si>
     <t>Autocrat</t>
   </si>
   <si>
@@ -68,15 +66,9 @@
     <t>Communism</t>
   </si>
   <si>
-    <t>Ultravisionary Socialism</t>
-  </si>
-  <si>
     <t>Communism Military Authority</t>
   </si>
   <si>
-    <t>Socio Kaiserism Military Authority</t>
-  </si>
-  <si>
     <t>Automated Communism</t>
   </si>
   <si>
@@ -116,9 +108,6 @@
     <t>Herzlandish Conservatism</t>
   </si>
   <si>
-    <t>Reflectivism</t>
-  </si>
-  <si>
     <t>Authoritarian Democracy</t>
   </si>
   <si>
@@ -140,18 +129,12 @@
     <t>Democratic Military Authority</t>
   </si>
   <si>
-    <t>Digital Technocracy</t>
-  </si>
-  <si>
     <t>Despotism</t>
   </si>
   <si>
     <t>Lorissian Kaiserism</t>
   </si>
   <si>
-    <t>Democratic-Kaiserism Military Authority</t>
-  </si>
-  <si>
     <t>Anarcho-Communism</t>
   </si>
   <si>
@@ -221,9 +204,6 @@
     <t>Supremacist Military Authority</t>
   </si>
   <si>
-    <t>Digital Stratocracy</t>
-  </si>
-  <si>
     <t>Absolute Securocracy</t>
   </si>
   <si>
@@ -290,21 +270,6 @@
     <t>Conservative Corporatism (Auth-Dem)</t>
   </si>
   <si>
-    <t>Bipartisan Democracy (Soc Dem)</t>
-  </si>
-  <si>
-    <t>Bipartisan Democracy (Soc Lib)</t>
-  </si>
-  <si>
-    <t>Bipartisan Democracy (Market Lib)</t>
-  </si>
-  <si>
-    <t>Bipartisan Democracy (Conservative)</t>
-  </si>
-  <si>
-    <t>Bipartisan Democracy (Auth Dem)</t>
-  </si>
-  <si>
     <t>Technocracy (Soc Dem)</t>
   </si>
   <si>
@@ -314,9 +279,6 @@
     <t>Technoautocracy (Autocrat)</t>
   </si>
   <si>
-    <t>Technocracy (Auth-Dem)</t>
-  </si>
-  <si>
     <t>Technocracy (Conservative)</t>
   </si>
   <si>
@@ -342,22 +304,60 @@
   </si>
   <si>
     <t>Gestalt</t>
+  </si>
+  <si>
+    <t>Socialism Military Authority</t>
+  </si>
+  <si>
+    <t>Multipartisan Democracy (Soc Dem)</t>
+  </si>
+  <si>
+    <t>Multipartisan Democracy (Soc Lib)</t>
+  </si>
+  <si>
+    <t>Multipartisan Democracy (Market Lib)</t>
+  </si>
+  <si>
+    <t>Multipartisan Democracy (Conservative)</t>
+  </si>
+  <si>
+    <t>Multipartisan Democracy (Auth Dem)</t>
+  </si>
+  <si>
+    <t>Authoritarian Democratic</t>
+  </si>
+  <si>
+    <t>Technocracy
+(Auth-Dem)</t>
+  </si>
+  <si>
+    <t>Ultravisionary Oligarchy</t>
+  </si>
+  <si>
+    <t>Neoliberalism</t>
+  </si>
+  <si>
+    <t>Cosmopolitanism</t>
+  </si>
+  <si>
+    <t>Reflectivism (Roqualian Conservatism)</t>
+  </si>
+  <si>
+    <t>Reactionary Conservatism (Moderate)</t>
+  </si>
+  <si>
+    <t>Reactionary Conservative (Insurrectionary)</t>
+  </si>
+  <si>
+    <t>Not Applicable</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -401,7 +401,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="20">
+  <fills count="29">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -423,12 +423,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF8A8FEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBD5D5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -516,8 +510,68 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFABEBF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D4D5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2DAE0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAEED2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F1D7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1E3FB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2E5EA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6E6E6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6D8D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAF2DF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="32">
+  <borders count="43">
     <border>
       <left/>
       <right/>
@@ -726,43 +780,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -917,10 +934,12 @@
         <color theme="1"/>
       </left>
       <right/>
-      <top style="medium">
+      <top style="thin">
         <color theme="1"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -928,189 +947,543 @@
       <right style="medium">
         <color theme="1"/>
       </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
       <top style="medium">
-        <color theme="1"/>
+        <color indexed="64"/>
       </top>
-      <bottom/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="162">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="33" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="34" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="34" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="34" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="32" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="36" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="38" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1121,16 +1494,16 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFDAF2DF"/>
       <color rgb="FF34994A"/>
-      <color rgb="FF992620"/>
-      <color rgb="FF999999"/>
-      <color rgb="FF6D7E99"/>
-      <color rgb="FF0E4899"/>
-      <color rgb="FF998B25"/>
-      <color rgb="FF996E12"/>
-      <color rgb="FF993650"/>
-      <color rgb="FF99181B"/>
-      <color rgb="FF990B0D"/>
+      <color rgb="FFF6D8D6"/>
+      <color rgb="FFE6E6E6"/>
+      <color rgb="FFE2E5EA"/>
+      <color rgb="FFD1E3FB"/>
+      <color rgb="FFF5F1D7"/>
+      <color rgb="FFFAEED2"/>
+      <color rgb="FFF2DAE0"/>
+      <color rgb="FFF8D4D5"/>
     </mruColors>
   </colors>
   <extLst>
@@ -1149,13 +1522,13 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>838083</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>133</xdr:colOff>
+      <xdr:colOff>1882</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>1540</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>950750</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -1173,15 +1546,20 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2381250" y="1238133"/>
-          <a:ext cx="952633" cy="838317"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2991904" y="1285344"/>
+          <a:ext cx="948868" cy="835004"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1217,14 +1595,19 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2381250" y="2914650"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2990850" y="3800475"/>
           <a:ext cx="952633" cy="838317"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1238,13 +1621,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>133</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>117</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1280,148 +1663,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>838083</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>133</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94724E27-3F2D-9767-5C75-C0628215EE01}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4810125" y="1238133"/>
-          <a:ext cx="952633" cy="838317"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>133</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>117</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DCB37140-6E14-5996-DBC6-160372C90823}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5419725" y="990600"/>
-          <a:ext cx="952633" cy="838317"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1476242</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>117</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2821AED1-5C4F-9A86-A626-4D406BD89045}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2990717" y="8782050"/>
-          <a:ext cx="952633" cy="838317"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>133</xdr:colOff>
+      <xdr:colOff>132</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>117</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1437,15 +1688,20 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7239000" y="2076450"/>
-          <a:ext cx="952633" cy="838317"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7848600" y="2123958"/>
+          <a:ext cx="952632" cy="838317"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1481,14 +1737,19 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9667875" y="2076450"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10277475" y="2124075"/>
           <a:ext cx="952633" cy="838317"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1525,14 +1786,19 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="12096750" y="2076450"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12706350" y="2124075"/>
           <a:ext cx="952633" cy="838317"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1569,14 +1835,19 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14525625" y="2076450"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15135225" y="2124075"/>
           <a:ext cx="952633" cy="838317"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1613,14 +1884,19 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="16954500" y="2076450"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17564100" y="2124075"/>
           <a:ext cx="952633" cy="838317"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1633,13 +1909,13 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>941</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>133</xdr:colOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>951691</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>117</xdr:rowOff>
     </xdr:to>
@@ -1657,15 +1933,20 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14525625" y="400050"/>
-          <a:ext cx="952633" cy="838317"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15124984" y="447261"/>
+          <a:ext cx="950750" cy="836660"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1701,50 +1982,6 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2381250" y="4591050"/>
-          <a:ext cx="952633" cy="838317"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>133</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>117</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="40" name="Picture 39">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C3E4E243-0AE3-3AF2-6AA4-C153C9A9BAA7}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
         <a:stretch>
           <a:fillRect/>
@@ -1752,8 +1989,57 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7239000" y="1238250"/>
-          <a:ext cx="952633" cy="838317"/>
+          <a:off x="2381250" y="4591050"/>
+          <a:ext cx="952633" cy="838317"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>941</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>951692</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>117</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="40" name="Picture 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C3E4E243-0AE3-3AF2-6AA4-C153C9A9BAA7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7844571" y="1283804"/>
+          <a:ext cx="950751" cy="836661"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1789,14 +2075,19 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9667875" y="1238250"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10277475" y="1285875"/>
           <a:ext cx="952633" cy="838317"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1833,14 +2124,19 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="12096750" y="1238250"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12706350" y="1285875"/>
           <a:ext cx="952633" cy="838317"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1877,14 +2173,19 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14525625" y="1238250"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15135225" y="1285875"/>
           <a:ext cx="952633" cy="838317"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1921,58 +2222,19 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="16954500" y="1238250"/>
-          <a:ext cx="952633" cy="838317"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>1476242</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>117</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="45" name="Picture 44">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F55579E2-8F25-0B21-5BC3-51D7CA051FDF}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="17563967" y="4591050"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17564100" y="1285875"/>
           <a:ext cx="952633" cy="838317"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2009,14 +2271,19 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="16954500" y="3752850"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17564100" y="3800475"/>
           <a:ext cx="952633" cy="838317"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2029,13 +2296,13 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>941</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>133</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>951691</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>117</xdr:rowOff>
     </xdr:to>
@@ -2053,15 +2320,20 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9667875" y="400050"/>
-          <a:ext cx="952633" cy="838317"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10271376" y="447261"/>
+          <a:ext cx="950750" cy="836660"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2073,13 +2345,13 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>941</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>133</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>951691</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>117</xdr:rowOff>
     </xdr:to>
@@ -2097,15 +2369,20 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="12096750" y="400050"/>
-          <a:ext cx="952633" cy="838317"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12698180" y="447261"/>
+          <a:ext cx="950750" cy="836660"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2117,13 +2394,13 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>941</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>133</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>951691</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>117</xdr:rowOff>
     </xdr:to>
@@ -2141,15 +2418,20 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7239000" y="400050"/>
-          <a:ext cx="952633" cy="838317"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7844571" y="447261"/>
+          <a:ext cx="950750" cy="836660"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2185,14 +2467,19 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="12706217" y="6267333"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12706217" y="7153158"/>
           <a:ext cx="952633" cy="838317"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2229,7 +2516,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2273,7 +2560,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2317,7 +2604,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2361,182 +2648,6 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="19383375" y="10458450"/>
-          <a:ext cx="952633" cy="838317"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>1476242</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>117</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="56" name="Picture 55">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A011143-7FAE-956B-286A-16CF037EA639}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="21812117" y="400050"/>
-          <a:ext cx="952633" cy="838317"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>1476242</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>117</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="57" name="Picture 56">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF2EE995-DDA6-0A22-EE96-0516C8EA947B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="19383242" y="2076450"/>
-          <a:ext cx="952633" cy="838317"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>133</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>117</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="58" name="Picture 57">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{775DC9BB-84D3-24D1-C1FE-B034B9DE3901}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="22421850" y="5429250"/>
-          <a:ext cx="952633" cy="838317"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>838083</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>133</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="59" name="Picture 58">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2C17876-C4F3-009D-A7DE-84E3B86953F8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId24"/>
         <a:stretch>
           <a:fillRect/>
@@ -2544,6 +2655,138 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
+          <a:off x="19383375" y="10458450"/>
+          <a:ext cx="952633" cy="838317"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>1476242</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>117</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="56" name="Picture 55">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A011143-7FAE-956B-286A-16CF037EA639}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId25"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21812117" y="400050"/>
+          <a:ext cx="952633" cy="838317"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>1476242</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>117</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="57" name="Picture 56">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF2EE995-DDA6-0A22-EE96-0516C8EA947B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19383242" y="2076450"/>
+          <a:ext cx="952633" cy="838317"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>838083</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>133</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="59" name="Picture 58">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2C17876-C4F3-009D-A7DE-84E3B86953F8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
           <a:off x="21812250" y="2076333"/>
           <a:ext cx="952633" cy="838317"/>
         </a:xfrm>
@@ -2581,7 +2824,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId25"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId28"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2625,7 +2868,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId29"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2669,7 +2912,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId30"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2713,7 +2956,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId28"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId31"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2757,7 +3000,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId29"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId32"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2801,7 +3044,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId30"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId33"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2845,7 +3088,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId31"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId34"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2889,7 +3132,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId32"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId35"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2933,7 +3176,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId33"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId36"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2941,6 +3184,280 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="19383375" y="7943850"/>
+          <a:ext cx="952633" cy="838317"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>838083</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>133</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="69" name="Picture 68">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{95A7ACFB-023A-285E-02E5-76789612CD70}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId37">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17564100" y="10505958"/>
+          <a:ext cx="952633" cy="838317"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>133</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>117</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="70" name="Picture 69">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F63461EB-BC72-D857-D654-E1010D3677C2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId38"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19383375" y="400050"/>
+          <a:ext cx="952633" cy="838317"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>1476242</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>117</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="71" name="Picture 70">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F48B821-E2E4-AAF5-AF5B-B99116165CE9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId39">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17563967" y="9667875"/>
+          <a:ext cx="952633" cy="838317"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>133</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>117</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="72" name="Picture 71">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7AE1016-D2A4-837D-7B92-4F34FF60CB32}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId40"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19992975" y="12134850"/>
+          <a:ext cx="952633" cy="838317"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>1476242</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>838083</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="73" name="Picture 72">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D782B29C-443A-8D00-38C9-AA643431FBD6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId41"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19383242" y="6267333"/>
+          <a:ext cx="952633" cy="838317"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>838083</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>133</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="74" name="Picture 73">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15A17062-D8F5-018C-2343-F6A710B52848}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId42"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19383375" y="3752733"/>
           <a:ext cx="952633" cy="838317"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2965,270 +3482,6 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="69" name="Picture 68">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{95A7ACFB-023A-285E-02E5-76789612CD70}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId34"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="16954500" y="8782050"/>
-          <a:ext cx="952633" cy="838317"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>133</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>117</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="70" name="Picture 69">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F63461EB-BC72-D857-D654-E1010D3677C2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId35"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="19383375" y="400050"/>
-          <a:ext cx="952633" cy="838317"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>1476242</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>117</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="71" name="Picture 70">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F48B821-E2E4-AAF5-AF5B-B99116165CE9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId36"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="17563967" y="10458450"/>
-          <a:ext cx="952633" cy="838317"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>133</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>117</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="72" name="Picture 71">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7AE1016-D2A4-837D-7B92-4F34FF60CB32}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId37"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="19992975" y="12134850"/>
-          <a:ext cx="952633" cy="838317"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>1476242</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>838083</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="73" name="Picture 72">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D782B29C-443A-8D00-38C9-AA643431FBD6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId38"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="19383242" y="6267333"/>
-          <a:ext cx="952633" cy="838317"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>838083</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>133</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="74" name="Picture 73">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15A17062-D8F5-018C-2343-F6A710B52848}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId39"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="19383375" y="3752733"/>
-          <a:ext cx="952633" cy="838317"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>133</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>117</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
         <xdr:cNvPr id="76" name="Picture 75">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
@@ -3241,14 +3494,19 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId40"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="17564100" y="9620250"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId43">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17564100" y="8829675"/>
           <a:ext cx="952633" cy="838317"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3285,7 +3543,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId41"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId44"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3329,138 +3587,6 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId42"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="19383375" y="4591050"/>
-          <a:ext cx="952633" cy="838317"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>1476242</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>117</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="80" name="Picture 79">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7ADA591-3D30-031A-0455-A1F8D2D54D73}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId43"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="19992842" y="5429250"/>
-          <a:ext cx="952633" cy="838317"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>838083</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>133</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="81" name="Picture 80">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D273B8C-F98C-2FE8-D4B8-A94A6ABA5D84}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId44"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2381250" y="2076333"/>
-          <a:ext cx="952633" cy="838317"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1476242</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>838083</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="82" name="Picture 81">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79FF78EE-EFFA-A75E-46FE-46A393B274BD}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId45"/>
         <a:stretch>
           <a:fillRect/>
@@ -3468,35 +3594,35 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4809992" y="2076333"/>
-          <a:ext cx="952633" cy="838317"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>838083</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
+          <a:off x="19383375" y="4591050"/>
+          <a:ext cx="952633" cy="838317"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>133</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="83" name="Picture 82">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1FBE676-8841-FE45-0C1B-E3D8092832B4}"/>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>117</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="80" name="Picture 79">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7ADA591-3D30-031A-0455-A1F8D2D54D73}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3512,46 +3638,1552 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2381250" y="7943733"/>
-          <a:ext cx="952633" cy="838317"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:oneCellAnchor>
+          <a:off x="19992975" y="9667875"/>
+          <a:ext cx="952633" cy="838317"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>1882</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>1539</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>950750</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="81" name="Picture 80">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D273B8C-F98C-2FE8-D4B8-A94A6ABA5D84}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId47">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2991904" y="2121887"/>
+          <a:ext cx="948868" cy="835004"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2785</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>1539</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>951653</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="82" name="Picture 81">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79FF78EE-EFFA-A75E-46FE-46A393B274BD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId48">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5419611" y="2121887"/>
+          <a:ext cx="948868" cy="835004"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1474172</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="952633" cy="838317"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="87" name="Picture 86">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A632083E-3974-4BDE-9532-69FD871F0034}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>1774</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F5B6F883-A774-7B15-32B0-6D644C214E48}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId49"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2990850" y="990600"/>
+          <a:off x="2989889" y="447261"/>
+          <a:ext cx="952633" cy="838317"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>246704</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>133</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="Picture 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C821A9A4-5548-6437-8371-C70B3A809DD9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId50"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5416826" y="445487"/>
+          <a:ext cx="952633" cy="838317"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>133</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>1773</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="Picture 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{935F18C1-0E85-EE43-8A45-E98E7FA005E5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId51">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5416826" y="1283804"/>
+          <a:ext cx="952633" cy="838317"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>133</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>1774</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="20" name="Picture 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{70D660EF-B146-36B9-1CB9-AA044C068769}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId52"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5416826" y="3793435"/>
+          <a:ext cx="952633" cy="838317"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>133</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>1773</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="21" name="Picture 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F6286A1-F05B-4981-12A5-AE3C0E3FF5A9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId53"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5416826" y="4629978"/>
+          <a:ext cx="952633" cy="838317"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1474172</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>1773</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="37" name="Picture 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4CAC2199-2F80-047D-5BD4-8498C7053887}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId54"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2989889" y="7976152"/>
+          <a:ext cx="952633" cy="838317"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>1474172</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>1774</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="38" name="Picture 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E220CBC-0620-1222-F58F-0EA87F4765B1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId55"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17550715" y="447261"/>
+          <a:ext cx="952633" cy="838317"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1476242</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>117</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="77" name="Picture 76">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2FD861A-2A13-5A85-4C07-3A772EE3FEE8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId56"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7848467" y="7153275"/>
+          <a:ext cx="952633" cy="838317"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>133</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>117</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="84" name="Picture 83">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD9F9A95-52D6-B802-43EC-AFD88FE10494}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId57"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10277475" y="7153275"/>
+          <a:ext cx="952633" cy="838317"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>1476242</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>117</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="86" name="Picture 85">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B656648-2A5E-C499-18C4-C1E5D9D6D8BA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId58"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15135092" y="7153275"/>
+          <a:ext cx="952633" cy="838317"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>133</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>117</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="88" name="Picture 87">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F7F7A04-D205-1F36-B74D-44DCDC2D8E4D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId59"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17564100" y="7153275"/>
+          <a:ext cx="952633" cy="838317"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>133</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>117</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="89" name="Picture 88">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{41E18C57-CEF3-4081-C575-A0023B92B816}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId60"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7848600" y="3800475"/>
+          <a:ext cx="952633" cy="838317"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>133</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>117</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="90" name="Picture 89">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7066E6F6-A1F5-128F-879A-A02A294D2DAF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId61"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10277475" y="3800475"/>
+          <a:ext cx="952633" cy="838317"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>133</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>117</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="93" name="Picture 92">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9552FC7B-456A-630C-7B19-1CD5EC1E1222}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId62"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12706350" y="3800475"/>
+          <a:ext cx="952633" cy="838317"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>133</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>117</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="94" name="Picture 93">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D375E670-5732-5531-50F2-C87654586349}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId63"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15135225" y="3800475"/>
+          <a:ext cx="952633" cy="838317"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="952633" cy="838317"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="97" name="Picture 96">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F8D2FE7-1524-4A19-A3FD-B9AAA48EFF8B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId57"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10277475" y="7153275"/>
+          <a:ext cx="952633" cy="838317"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>133</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>117</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="100" name="Picture 99">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3DEE67E-B881-C4B7-577F-38B85E39626D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId64"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7848600" y="5476875"/>
+          <a:ext cx="952633" cy="838317"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>133</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>117</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="101" name="Picture 100">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2070C39-AD24-2462-B05F-292D3F4F0114}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId65"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10277475" y="5476875"/>
+          <a:ext cx="952633" cy="838317"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>941</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>837966</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>1074</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>838083</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C6775750-44D3-29C9-4CAD-007110B2E576}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId66"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12707291" y="5476641"/>
+          <a:ext cx="952633" cy="838317"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>1475433</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>1773</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>951691</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>1890</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E989CE1E-8611-A309-1C11-9058D60D8C26}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId67"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15134283" y="5478648"/>
+          <a:ext cx="952633" cy="838317"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>133</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>117</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1FD04ECB-386A-C54D-A98A-7814D79CAC8E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId68"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17564100" y="5476875"/>
+          <a:ext cx="952633" cy="838317"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>941</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>837849</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>1074</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>837966</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D28AE48-8A62-CE7A-DA59-C3A970E09183}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId69"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12707291" y="7991124"/>
+          <a:ext cx="952633" cy="838317"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>133</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>117</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="Picture 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{499559D2-E645-8885-752C-C8512E5F802A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId70"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7848600" y="7991475"/>
+          <a:ext cx="952633" cy="838317"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>133</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>117</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="22" name="Picture 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C1871EF-E2A9-718B-143F-6D5F2423366E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId71"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10277475" y="7991475"/>
+          <a:ext cx="952633" cy="838317"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>133</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>117</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="23" name="Picture 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7FE353EC-EE40-8A06-F000-934281B1DDCC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId72"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15135225" y="7991475"/>
+          <a:ext cx="952633" cy="838317"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>10830</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>133</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>10947</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="24" name="Picture 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{95442427-E803-CF9F-A8B6-78F3AA5E434D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId73"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17564100" y="8002305"/>
+          <a:ext cx="952633" cy="838317"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>133</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>117</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="25" name="Picture 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{011ECE00-E589-6633-FC57-C797C2B45329}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId74"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15135225" y="6315075"/>
+          <a:ext cx="952633" cy="838317"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>133</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>117</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="26" name="Picture 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F839796-DEFC-2813-5392-586A2D1CB4D4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId75"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17564100" y="6315075"/>
+          <a:ext cx="952633" cy="838317"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>133</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>117</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="27" name="Picture 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F32C256B-A14F-5654-F5C1-D4E4ACCDB6B2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId76"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10277475" y="6315075"/>
+          <a:ext cx="952633" cy="838317"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1475433</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>1890</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>951691</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>2007</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="28" name="Picture 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65F7CA2E-1EB1-416C-6580-35A4D05A24C9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId77"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7847658" y="6316965"/>
+          <a:ext cx="952633" cy="838317"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>1475433</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>837966</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>951691</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>838083</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="29" name="Picture 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7138378-8E92-2CA8-919D-6A65A781F7F3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId78"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15134283" y="8829441"/>
+          <a:ext cx="952633" cy="838317"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>133</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>117</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="30" name="Picture 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8922BB1-0B22-EDC5-C5F6-82946F46C44E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId79"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15135225" y="9667875"/>
+          <a:ext cx="952633" cy="838317"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="952633" cy="838317"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="96" name="Picture 95">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A9DF7DD4-B061-45FE-B59D-698E33429F74}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId79"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15135225" y="9667875"/>
           <a:ext cx="952633" cy="838317"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3881,7 +5513,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36B20B63-D92D-4572-9E4D-A5DC1291D4FF}">
-  <dimension ref="B1:V40"/>
+  <dimension ref="B1:V41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -3909,692 +5541,724 @@
   <sheetData>
     <row r="1" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C2" s="50" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="51"/>
-      <c r="E2" s="52" t="s">
+      <c r="C2" s="142" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="53"/>
-      <c r="G2" s="54" t="s">
+      <c r="D2" s="143"/>
+      <c r="E2" s="144" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="145"/>
+      <c r="G2" s="146" t="s">
         <v>0</v>
       </c>
-      <c r="H2" s="55"/>
-      <c r="I2" s="56" t="s">
+      <c r="H2" s="147"/>
+      <c r="I2" s="148" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="57"/>
-      <c r="K2" s="58" t="s">
+      <c r="J2" s="149"/>
+      <c r="K2" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="L2" s="59"/>
-      <c r="M2" s="60" t="s">
+      <c r="L2" s="151"/>
+      <c r="M2" s="152" t="s">
         <v>3</v>
       </c>
-      <c r="N2" s="61"/>
-      <c r="O2" s="62" t="s">
+      <c r="N2" s="153"/>
+      <c r="O2" s="154" t="s">
+        <v>94</v>
+      </c>
+      <c r="P2" s="155"/>
+      <c r="Q2" s="156" t="s">
         <v>4</v>
       </c>
-      <c r="P2" s="63"/>
-      <c r="Q2" s="64" t="s">
+      <c r="R2" s="157"/>
+      <c r="S2" s="158" t="s">
         <v>5</v>
       </c>
-      <c r="R2" s="65"/>
-      <c r="S2" s="66" t="s">
-        <v>6</v>
-      </c>
-      <c r="T2" s="67"/>
-      <c r="U2" s="68" t="s">
-        <v>100</v>
-      </c>
-      <c r="V2" s="69"/>
+      <c r="T2" s="159"/>
+      <c r="U2" s="160" t="s">
+        <v>87</v>
+      </c>
+      <c r="V2" s="161"/>
     </row>
     <row r="3" spans="2:22" ht="66" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="C3" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="D3" s="12"/>
-      <c r="E3" s="49" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="12"/>
-      <c r="G3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="2"/>
-      <c r="I3" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="J3" s="2"/>
-      <c r="K3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L3" s="2"/>
-      <c r="M3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="N3" s="2"/>
-      <c r="O3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="3" t="s">
+      <c r="B3" s="105" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" s="20"/>
+      <c r="E3" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="31"/>
+      <c r="G3" s="38" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="39"/>
+      <c r="I3" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="R3" s="2"/>
-      <c r="S3" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="T3" s="2"/>
-      <c r="U3" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="V3" s="2"/>
+      <c r="J3" s="47"/>
+      <c r="K3" s="54" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3" s="55"/>
+      <c r="M3" s="62" t="s">
+        <v>35</v>
+      </c>
+      <c r="N3" s="63"/>
+      <c r="O3" s="70" t="s">
+        <v>22</v>
+      </c>
+      <c r="P3" s="71"/>
+      <c r="Q3" s="78" t="s">
+        <v>29</v>
+      </c>
+      <c r="R3" s="79"/>
+      <c r="S3" s="86" t="s">
+        <v>48</v>
+      </c>
+      <c r="T3" s="127"/>
+      <c r="U3" s="140" t="s">
+        <v>55</v>
+      </c>
+      <c r="V3" s="141"/>
     </row>
     <row r="4" spans="2:22" ht="66" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="15"/>
-      <c r="C4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="7" t="s">
+      <c r="B4" s="106"/>
+      <c r="C4" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="22"/>
+      <c r="E4" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="32"/>
+      <c r="G4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="4"/>
+      <c r="I4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="4"/>
+      <c r="K4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L4" s="4"/>
+      <c r="M4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="8"/>
-      <c r="I4" s="7" t="s">
+      <c r="N4" s="4"/>
+      <c r="O4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="8"/>
-      <c r="K4" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="L4" s="8"/>
-      <c r="M4" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="N4" s="8"/>
-      <c r="O4" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="P4" s="8"/>
-      <c r="Q4" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="R4" s="1"/>
-      <c r="S4" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="T4" s="1"/>
-      <c r="U4" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="V4" s="1"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="80" t="s">
+        <v>41</v>
+      </c>
+      <c r="R4" s="81"/>
+      <c r="S4" s="87" t="s">
+        <v>49</v>
+      </c>
+      <c r="T4" s="128"/>
+      <c r="U4" s="133" t="s">
+        <v>56</v>
+      </c>
+      <c r="V4" s="96"/>
     </row>
     <row r="5" spans="2:22" ht="66" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="16"/>
-      <c r="C5" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="H5" s="6"/>
-      <c r="I5" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="J5" s="6"/>
-      <c r="K5" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="L5" s="6"/>
-      <c r="M5" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="N5" s="6"/>
-      <c r="O5" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="P5" s="6"/>
-      <c r="Q5" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="R5" s="1"/>
-      <c r="S5" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="T5" s="1"/>
-      <c r="U5" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="V5" s="1"/>
+      <c r="B5" s="107"/>
+      <c r="C5" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="22"/>
+      <c r="E5" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="32"/>
+      <c r="G5" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H5" s="2"/>
+      <c r="I5" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="J5" s="2"/>
+      <c r="K5" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L5" s="2"/>
+      <c r="M5" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N5" s="2"/>
+      <c r="O5" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="80" t="s">
+        <v>45</v>
+      </c>
+      <c r="R5" s="81"/>
+      <c r="S5" s="87" t="s">
+        <v>50</v>
+      </c>
+      <c r="T5" s="128"/>
+      <c r="U5" s="133" t="s">
+        <v>57</v>
+      </c>
+      <c r="V5" s="96"/>
     </row>
     <row r="6" spans="2:22" ht="66" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="N6" s="10"/>
-      <c r="O6" s="9"/>
-      <c r="P6" s="10"/>
-      <c r="Q6" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="R6" s="10"/>
-      <c r="S6" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="T6" s="10"/>
-      <c r="U6" s="9"/>
-      <c r="V6" s="10"/>
+      <c r="B6" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="5"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="R6" s="6"/>
+      <c r="S6" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="T6" s="129"/>
+      <c r="U6" s="134"/>
+      <c r="V6" s="135"/>
     </row>
     <row r="7" spans="2:22" ht="66" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="R7" s="8"/>
-      <c r="S7" s="7" t="s">
+      <c r="B7" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F7" s="4"/>
+      <c r="G7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="4"/>
+      <c r="I7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J7" s="4"/>
+      <c r="K7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L7" s="4"/>
+      <c r="M7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="R7" s="4"/>
+      <c r="S7" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="T7" s="130"/>
+      <c r="U7" s="136" t="s">
         <v>59</v>
       </c>
-      <c r="T7" s="8"/>
-      <c r="U7" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="V7" s="8"/>
+      <c r="V7" s="137"/>
     </row>
     <row r="8" spans="2:22" ht="66" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="10"/>
-      <c r="M8" s="9"/>
-      <c r="N8" s="10"/>
-      <c r="O8" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="P8" s="10"/>
-      <c r="Q8" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="R8" s="10"/>
-      <c r="S8" s="9" t="s">
+      <c r="B8" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="5"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="6"/>
+      <c r="Q8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="R8" s="6"/>
+      <c r="S8" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="T8" s="129"/>
+      <c r="U8" s="134" t="s">
         <v>58</v>
       </c>
-      <c r="T8" s="10"/>
-      <c r="U8" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="V8" s="10"/>
+      <c r="V8" s="135"/>
     </row>
     <row r="9" spans="2:22" ht="66" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="C9" s="45" t="s">
+      <c r="B9" s="99" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D9" s="16"/>
+      <c r="E9" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="F9" s="16"/>
+      <c r="G9" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="H9" s="16"/>
+      <c r="I9" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="J9" s="16"/>
+      <c r="K9" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="L9" s="16"/>
+      <c r="M9" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="N9" s="16"/>
+      <c r="O9" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="D9" s="46"/>
-      <c r="E9" s="47" t="s">
-        <v>96</v>
-      </c>
-      <c r="F9" s="46"/>
-      <c r="G9" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="H9" s="46"/>
-      <c r="I9" s="47" t="s">
-        <v>94</v>
-      </c>
-      <c r="J9" s="46"/>
-      <c r="K9" s="47" t="s">
-        <v>93</v>
-      </c>
-      <c r="L9" s="46"/>
-      <c r="M9" s="47" t="s">
-        <v>92</v>
-      </c>
-      <c r="N9" s="46"/>
-      <c r="O9" s="47" t="s">
-        <v>91</v>
-      </c>
-      <c r="P9" s="46"/>
-      <c r="Q9" s="47" t="s">
-        <v>90</v>
-      </c>
-      <c r="R9" s="46"/>
-      <c r="S9" s="47" t="s">
-        <v>89</v>
-      </c>
-      <c r="T9" s="46"/>
-      <c r="U9" s="4"/>
-      <c r="V9" s="1"/>
+      <c r="P9" s="16"/>
+      <c r="Q9" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="R9" s="16"/>
+      <c r="S9" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="T9" s="131"/>
+      <c r="U9" s="133"/>
+      <c r="V9" s="96"/>
     </row>
     <row r="10" spans="2:22" ht="66" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="21"/>
-      <c r="C10" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="1"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="39" t="s">
+      <c r="B10" s="100"/>
+      <c r="C10" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="22"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="H10" s="10"/>
+      <c r="I10" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="J10" s="10"/>
+      <c r="K10" s="108" t="s">
+        <v>102</v>
+      </c>
+      <c r="L10" s="109"/>
+      <c r="M10" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="H10" s="40"/>
-      <c r="I10" s="39" t="s">
+      <c r="N10" s="14"/>
+      <c r="O10" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="J10" s="40"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="43" t="s">
-        <v>81</v>
-      </c>
-      <c r="N10" s="44"/>
-      <c r="O10" s="43" t="s">
-        <v>82</v>
-      </c>
-      <c r="P10" s="44"/>
-      <c r="Q10" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="R10" s="1"/>
-      <c r="S10" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="T10" s="1"/>
-      <c r="U10" s="4"/>
-      <c r="V10" s="1"/>
+      <c r="P10" s="14"/>
+      <c r="Q10" s="80" t="s">
+        <v>40</v>
+      </c>
+      <c r="R10" s="81"/>
+      <c r="S10" s="87" t="s">
+        <v>54</v>
+      </c>
+      <c r="T10" s="128"/>
+      <c r="U10" s="133"/>
+      <c r="V10" s="96"/>
     </row>
     <row r="11" spans="2:22" ht="66" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="21"/>
-      <c r="C11" s="48" t="s">
-        <v>98</v>
-      </c>
-      <c r="D11" s="42"/>
-      <c r="E11" s="41" t="s">
-        <v>16</v>
-      </c>
-      <c r="F11" s="42"/>
-      <c r="G11" s="41" t="s">
-        <v>77</v>
-      </c>
-      <c r="H11" s="42"/>
-      <c r="I11" s="41" t="s">
-        <v>76</v>
-      </c>
-      <c r="J11" s="42"/>
-      <c r="K11" s="41" t="s">
-        <v>78</v>
-      </c>
-      <c r="L11" s="42"/>
-      <c r="M11" s="41" t="s">
-        <v>79</v>
-      </c>
-      <c r="N11" s="42"/>
-      <c r="O11" s="41" t="s">
-        <v>80</v>
-      </c>
-      <c r="P11" s="42"/>
-      <c r="Q11" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="R11" s="1"/>
-      <c r="S11" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="T11" s="1"/>
-      <c r="U11" s="4"/>
-      <c r="V11" s="1"/>
+      <c r="B11" s="100"/>
+      <c r="C11" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="D11" s="12"/>
+      <c r="E11" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="12"/>
+      <c r="G11" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="H11" s="12"/>
+      <c r="I11" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="J11" s="12"/>
+      <c r="K11" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="L11" s="12"/>
+      <c r="M11" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="N11" s="12"/>
+      <c r="O11" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="P11" s="12"/>
+      <c r="Q11" s="80" t="s">
+        <v>46</v>
+      </c>
+      <c r="R11" s="81"/>
+      <c r="S11" s="87"/>
+      <c r="T11" s="128"/>
+      <c r="U11" s="133"/>
+      <c r="V11" s="96"/>
     </row>
     <row r="12" spans="2:22" ht="66" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="21"/>
-      <c r="C12" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="D12" s="1"/>
-      <c r="E12" s="4" t="s">
+      <c r="B12" s="100"/>
+      <c r="C12" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="22"/>
+      <c r="E12" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="F12" s="32"/>
+      <c r="G12" s="40" t="s">
+        <v>86</v>
+      </c>
+      <c r="H12" s="41"/>
+      <c r="I12" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="J12" s="49"/>
+      <c r="K12" s="56" t="s">
         <v>97</v>
       </c>
-      <c r="F12" s="1"/>
-      <c r="G12" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="H12" s="1"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L12" s="1"/>
-      <c r="M12" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="N12" s="1"/>
-      <c r="O12" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="P12" s="1"/>
-      <c r="Q12" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="R12" s="1"/>
-      <c r="S12" s="4"/>
-      <c r="T12" s="1"/>
-      <c r="U12" s="4"/>
-      <c r="V12" s="1"/>
+      <c r="L12" s="57"/>
+      <c r="M12" s="64" t="s">
+        <v>100</v>
+      </c>
+      <c r="N12" s="65"/>
+      <c r="O12" s="72" t="s">
+        <v>101</v>
+      </c>
+      <c r="P12" s="73"/>
+      <c r="Q12" s="80" t="s">
+        <v>42</v>
+      </c>
+      <c r="R12" s="81"/>
+      <c r="S12" s="87"/>
+      <c r="T12" s="128"/>
+      <c r="U12" s="133"/>
+      <c r="V12" s="96"/>
     </row>
     <row r="13" spans="2:22" ht="66" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="21"/>
-      <c r="C13" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="1"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="4" t="s">
+      <c r="B13" s="100"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="48"/>
+      <c r="J13" s="49"/>
+      <c r="K13" s="56"/>
+      <c r="L13" s="57"/>
+      <c r="M13" s="64" t="s">
+        <v>21</v>
+      </c>
+      <c r="N13" s="65"/>
+      <c r="O13" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="N13" s="1"/>
-      <c r="O13" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="P13" s="1"/>
-      <c r="Q13" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="R13" s="1"/>
-      <c r="S13" s="4"/>
-      <c r="T13" s="1"/>
-      <c r="U13" s="4"/>
-      <c r="V13" s="1"/>
+      <c r="P13" s="73"/>
+      <c r="Q13" s="80" t="s">
+        <v>43</v>
+      </c>
+      <c r="R13" s="81"/>
+      <c r="S13" s="87"/>
+      <c r="T13" s="128"/>
+      <c r="U13" s="133"/>
+      <c r="V13" s="96"/>
     </row>
     <row r="14" spans="2:22" ht="66" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="21"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="N14" s="1"/>
-      <c r="O14" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="P14" s="1"/>
-      <c r="Q14" s="4"/>
-      <c r="R14" s="1"/>
-      <c r="S14" s="4"/>
-      <c r="T14" s="1"/>
-      <c r="U14" s="4"/>
-      <c r="V14" s="1"/>
+      <c r="B14" s="100"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="48"/>
+      <c r="J14" s="49"/>
+      <c r="K14" s="56"/>
+      <c r="L14" s="57"/>
+      <c r="M14" s="64" t="s">
+        <v>99</v>
+      </c>
+      <c r="N14" s="65"/>
+      <c r="O14" s="72" t="s">
+        <v>26</v>
+      </c>
+      <c r="P14" s="73"/>
+      <c r="Q14" s="80" t="s">
+        <v>96</v>
+      </c>
+      <c r="R14" s="81"/>
+      <c r="S14" s="87"/>
+      <c r="T14" s="128"/>
+      <c r="U14" s="133"/>
+      <c r="V14" s="96"/>
     </row>
     <row r="15" spans="2:22" ht="66" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="21"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="4"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="P15" s="1"/>
-      <c r="Q15" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="R15" s="1"/>
-      <c r="S15" s="4"/>
-      <c r="T15" s="1"/>
-      <c r="U15" s="4"/>
-      <c r="V15" s="1"/>
+      <c r="B15" s="100"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="48"/>
+      <c r="J15" s="49"/>
+      <c r="K15" s="56"/>
+      <c r="L15" s="57"/>
+      <c r="M15" s="64"/>
+      <c r="N15" s="65"/>
+      <c r="O15" s="72" t="s">
+        <v>24</v>
+      </c>
+      <c r="P15" s="73"/>
+      <c r="Q15" s="80" t="s">
+        <v>44</v>
+      </c>
+      <c r="R15" s="81"/>
+      <c r="S15" s="87"/>
+      <c r="T15" s="128"/>
+      <c r="U15" s="133"/>
+      <c r="V15" s="96"/>
     </row>
-    <row r="16" spans="2:22" ht="66" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="22"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="27"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="27"/>
-      <c r="I16" s="28"/>
-      <c r="J16" s="27"/>
-      <c r="K16" s="28"/>
-      <c r="L16" s="27"/>
-      <c r="M16" s="28"/>
-      <c r="N16" s="27"/>
-      <c r="O16" s="28"/>
-      <c r="P16" s="27"/>
-      <c r="Q16" s="28" t="s">
-        <v>53</v>
-      </c>
-      <c r="R16" s="27"/>
-      <c r="S16" s="28"/>
-      <c r="T16" s="27"/>
-      <c r="U16" s="28"/>
-      <c r="V16" s="27"/>
+    <row r="16" spans="2:22" ht="66" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="100"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="41"/>
+      <c r="I16" s="48"/>
+      <c r="J16" s="49"/>
+      <c r="K16" s="56"/>
+      <c r="L16" s="57"/>
+      <c r="M16" s="64"/>
+      <c r="N16" s="65"/>
+      <c r="O16" s="72"/>
+      <c r="P16" s="73"/>
+      <c r="Q16" s="80" t="s">
+        <v>47</v>
+      </c>
+      <c r="R16" s="81"/>
+      <c r="S16" s="87"/>
+      <c r="T16" s="128"/>
+      <c r="U16" s="133"/>
+      <c r="V16" s="96"/>
     </row>
-    <row r="17" spans="2:22" ht="66" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="C17" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="D17" s="30"/>
-      <c r="E17" s="31"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="31"/>
-      <c r="H17" s="30"/>
-      <c r="I17" s="31"/>
-      <c r="J17" s="30"/>
-      <c r="K17" s="31"/>
-      <c r="L17" s="30"/>
-      <c r="M17" s="31"/>
-      <c r="N17" s="30"/>
-      <c r="O17" s="31"/>
-      <c r="P17" s="30"/>
-      <c r="Q17" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="R17" s="30"/>
-      <c r="S17" s="31"/>
-      <c r="T17" s="30"/>
-      <c r="U17" s="31"/>
-      <c r="V17" s="32"/>
+    <row r="17" spans="2:22" ht="66" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="101"/>
+      <c r="C17" s="110"/>
+      <c r="D17" s="111"/>
+      <c r="E17" s="112"/>
+      <c r="F17" s="113"/>
+      <c r="G17" s="114"/>
+      <c r="H17" s="115"/>
+      <c r="I17" s="116"/>
+      <c r="J17" s="117"/>
+      <c r="K17" s="118"/>
+      <c r="L17" s="119"/>
+      <c r="M17" s="120"/>
+      <c r="N17" s="121"/>
+      <c r="O17" s="122"/>
+      <c r="P17" s="123"/>
+      <c r="Q17" s="124"/>
+      <c r="R17" s="125"/>
+      <c r="S17" s="126"/>
+      <c r="T17" s="132"/>
+      <c r="U17" s="138"/>
+      <c r="V17" s="139"/>
     </row>
     <row r="18" spans="2:22" ht="66" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="24"/>
-      <c r="C18" s="33"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="4"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="4"/>
-      <c r="N18" s="1"/>
-      <c r="O18" s="4"/>
-      <c r="P18" s="1"/>
-      <c r="Q18" s="4"/>
-      <c r="R18" s="1"/>
-      <c r="S18" s="4"/>
-      <c r="T18" s="1"/>
-      <c r="U18" s="4"/>
-      <c r="V18" s="34"/>
+      <c r="B18" s="102" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="26"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="50"/>
+      <c r="J18" s="51"/>
+      <c r="K18" s="58"/>
+      <c r="L18" s="59"/>
+      <c r="M18" s="66" t="s">
+        <v>37</v>
+      </c>
+      <c r="N18" s="67"/>
+      <c r="O18" s="74"/>
+      <c r="P18" s="75"/>
+      <c r="Q18" s="82" t="s">
+        <v>30</v>
+      </c>
+      <c r="R18" s="83"/>
+      <c r="S18" s="89"/>
+      <c r="T18" s="90"/>
+      <c r="U18" s="94"/>
+      <c r="V18" s="95"/>
     </row>
     <row r="19" spans="2:22" ht="66" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="24"/>
-      <c r="C19" s="33"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="4"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="4"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="4"/>
-      <c r="P19" s="1"/>
-      <c r="Q19" s="4"/>
-      <c r="R19" s="1"/>
-      <c r="S19" s="4"/>
-      <c r="T19" s="1"/>
-      <c r="U19" s="4"/>
-      <c r="V19" s="34"/>
+      <c r="B19" s="103"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="41"/>
+      <c r="I19" s="48"/>
+      <c r="J19" s="49"/>
+      <c r="K19" s="56"/>
+      <c r="L19" s="57"/>
+      <c r="M19" s="64" t="s">
+        <v>36</v>
+      </c>
+      <c r="N19" s="65"/>
+      <c r="O19" s="72"/>
+      <c r="P19" s="73"/>
+      <c r="Q19" s="80"/>
+      <c r="R19" s="81"/>
+      <c r="S19" s="87"/>
+      <c r="T19" s="88"/>
+      <c r="U19" s="93"/>
+      <c r="V19" s="96"/>
     </row>
     <row r="20" spans="2:22" ht="66" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="24"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="4"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="4"/>
-      <c r="N20" s="1"/>
-      <c r="O20" s="4"/>
-      <c r="P20" s="1"/>
-      <c r="Q20" s="4"/>
-      <c r="R20" s="1"/>
-      <c r="S20" s="4"/>
-      <c r="T20" s="1"/>
-      <c r="U20" s="4"/>
-      <c r="V20" s="34"/>
+      <c r="B20" s="103"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="48"/>
+      <c r="J20" s="49"/>
+      <c r="K20" s="56"/>
+      <c r="L20" s="57"/>
+      <c r="M20" s="64"/>
+      <c r="N20" s="65"/>
+      <c r="O20" s="72"/>
+      <c r="P20" s="73"/>
+      <c r="Q20" s="80"/>
+      <c r="R20" s="81"/>
+      <c r="S20" s="87"/>
+      <c r="T20" s="88"/>
+      <c r="U20" s="93"/>
+      <c r="V20" s="96"/>
     </row>
     <row r="21" spans="2:22" ht="66" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="24"/>
-      <c r="C21" s="33"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="4"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="4"/>
-      <c r="N21" s="1"/>
-      <c r="O21" s="4"/>
-      <c r="P21" s="1"/>
-      <c r="Q21" s="4"/>
-      <c r="R21" s="1"/>
-      <c r="S21" s="4"/>
-      <c r="T21" s="1"/>
-      <c r="U21" s="4"/>
-      <c r="V21" s="34"/>
+      <c r="B21" s="103"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="33"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="40"/>
+      <c r="H21" s="41"/>
+      <c r="I21" s="48"/>
+      <c r="J21" s="49"/>
+      <c r="K21" s="56"/>
+      <c r="L21" s="57"/>
+      <c r="M21" s="64"/>
+      <c r="N21" s="65"/>
+      <c r="O21" s="72"/>
+      <c r="P21" s="73"/>
+      <c r="Q21" s="80"/>
+      <c r="R21" s="81"/>
+      <c r="S21" s="87"/>
+      <c r="T21" s="88"/>
+      <c r="U21" s="93"/>
+      <c r="V21" s="96"/>
     </row>
-    <row r="22" spans="2:22" ht="66" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="25"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="37"/>
-      <c r="F22" s="36"/>
-      <c r="G22" s="37"/>
-      <c r="H22" s="36"/>
-      <c r="I22" s="37"/>
-      <c r="J22" s="36"/>
-      <c r="K22" s="37"/>
-      <c r="L22" s="36"/>
-      <c r="M22" s="37"/>
-      <c r="N22" s="36"/>
-      <c r="O22" s="37"/>
-      <c r="P22" s="36"/>
-      <c r="Q22" s="37"/>
-      <c r="R22" s="36"/>
-      <c r="S22" s="37"/>
-      <c r="T22" s="36"/>
-      <c r="U22" s="37"/>
-      <c r="V22" s="38"/>
+    <row r="22" spans="2:22" ht="66" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="103"/>
+      <c r="C22" s="27"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="40"/>
+      <c r="H22" s="41"/>
+      <c r="I22" s="48"/>
+      <c r="J22" s="49"/>
+      <c r="K22" s="56"/>
+      <c r="L22" s="57"/>
+      <c r="M22" s="64"/>
+      <c r="N22" s="65"/>
+      <c r="O22" s="72"/>
+      <c r="P22" s="73"/>
+      <c r="Q22" s="80"/>
+      <c r="R22" s="81"/>
+      <c r="S22" s="87"/>
+      <c r="T22" s="88"/>
+      <c r="U22" s="93"/>
+      <c r="V22" s="96"/>
     </row>
-    <row r="23" spans="2:22" ht="66" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="2:22" ht="66" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="104"/>
+      <c r="C23" s="28"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="37"/>
+      <c r="G23" s="44"/>
+      <c r="H23" s="45"/>
+      <c r="I23" s="52"/>
+      <c r="J23" s="53"/>
+      <c r="K23" s="60"/>
+      <c r="L23" s="61"/>
+      <c r="M23" s="68"/>
+      <c r="N23" s="69"/>
+      <c r="O23" s="76"/>
+      <c r="P23" s="77"/>
+      <c r="Q23" s="84"/>
+      <c r="R23" s="85"/>
+      <c r="S23" s="91"/>
+      <c r="T23" s="92"/>
+      <c r="U23" s="97"/>
+      <c r="V23" s="98"/>
+    </row>
     <row r="24" spans="2:22" ht="66" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" spans="2:22" ht="66" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="26" spans="2:22" ht="66" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4612,11 +6276,9 @@
     <row r="38" ht="66" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="39" ht="66" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="40" ht="66" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="66" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="S2:T2"/>
+  <mergeCells count="14">
     <mergeCell ref="U2:V2"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="K2:L2"/>
@@ -4625,8 +6287,12 @@
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="I2:J2"/>
-    <mergeCell ref="B9:B16"/>
-    <mergeCell ref="B17:B22"/>
+    <mergeCell ref="B18:B23"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="B9:B17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Ideologies List.xlsx
+++ b/Ideologies List.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -16,7 +16,6 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1333,39 +1332,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="28" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="19" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1426,6 +1392,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="28" borderId="38" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1450,17 +1443,14 @@
     <xf numFmtId="0" fontId="5" fillId="12" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="15" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1480,11 +1470,20 @@
     <xf numFmtId="0" fontId="5" fillId="17" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5541,49 +5540,49 @@
   <sheetData>
     <row r="1" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C2" s="142" t="s">
+      <c r="C2" s="140" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="143"/>
-      <c r="E2" s="144" t="s">
+      <c r="D2" s="141"/>
+      <c r="E2" s="142" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="145"/>
-      <c r="G2" s="146" t="s">
+      <c r="F2" s="143"/>
+      <c r="G2" s="144" t="s">
         <v>0</v>
       </c>
-      <c r="H2" s="147"/>
-      <c r="I2" s="148" t="s">
+      <c r="H2" s="145"/>
+      <c r="I2" s="146" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="149"/>
-      <c r="K2" s="150" t="s">
+      <c r="J2" s="147"/>
+      <c r="K2" s="136" t="s">
         <v>2</v>
       </c>
-      <c r="L2" s="151"/>
-      <c r="M2" s="152" t="s">
+      <c r="L2" s="137"/>
+      <c r="M2" s="138" t="s">
         <v>3</v>
       </c>
-      <c r="N2" s="153"/>
-      <c r="O2" s="154" t="s">
+      <c r="N2" s="139"/>
+      <c r="O2" s="151" t="s">
         <v>94</v>
       </c>
-      <c r="P2" s="155"/>
-      <c r="Q2" s="156" t="s">
+      <c r="P2" s="152"/>
+      <c r="Q2" s="153" t="s">
         <v>4</v>
       </c>
-      <c r="R2" s="157"/>
-      <c r="S2" s="158" t="s">
+      <c r="R2" s="154"/>
+      <c r="S2" s="155" t="s">
         <v>5</v>
       </c>
-      <c r="T2" s="159"/>
-      <c r="U2" s="160" t="s">
+      <c r="T2" s="156"/>
+      <c r="U2" s="131" t="s">
         <v>87</v>
       </c>
-      <c r="V2" s="161"/>
+      <c r="V2" s="132"/>
     </row>
     <row r="3" spans="2:22" ht="66" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="105" t="s">
+      <c r="B3" s="133" t="s">
         <v>62</v>
       </c>
       <c r="C3" s="19" t="s">
@@ -5621,14 +5620,14 @@
       <c r="S3" s="86" t="s">
         <v>48</v>
       </c>
-      <c r="T3" s="127"/>
-      <c r="U3" s="140" t="s">
+      <c r="T3" s="116"/>
+      <c r="U3" s="129" t="s">
         <v>55</v>
       </c>
-      <c r="V3" s="141"/>
+      <c r="V3" s="130"/>
     </row>
     <row r="4" spans="2:22" ht="66" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="106"/>
+      <c r="B4" s="134"/>
       <c r="C4" s="21" t="s">
         <v>31</v>
       </c>
@@ -5664,14 +5663,14 @@
       <c r="S4" s="87" t="s">
         <v>49</v>
       </c>
-      <c r="T4" s="128"/>
-      <c r="U4" s="133" t="s">
+      <c r="T4" s="117"/>
+      <c r="U4" s="122" t="s">
         <v>56</v>
       </c>
       <c r="V4" s="96"/>
     </row>
     <row r="5" spans="2:22" ht="66" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="107"/>
+      <c r="B5" s="135"/>
       <c r="C5" s="21" t="s">
         <v>32</v>
       </c>
@@ -5707,8 +5706,8 @@
       <c r="S5" s="87" t="s">
         <v>50</v>
       </c>
-      <c r="T5" s="128"/>
-      <c r="U5" s="133" t="s">
+      <c r="T5" s="117"/>
+      <c r="U5" s="122" t="s">
         <v>57</v>
       </c>
       <c r="V5" s="96"/>
@@ -5738,9 +5737,9 @@
       <c r="S6" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="T6" s="129"/>
-      <c r="U6" s="134"/>
-      <c r="V6" s="135"/>
+      <c r="T6" s="118"/>
+      <c r="U6" s="123"/>
+      <c r="V6" s="124"/>
     </row>
     <row r="7" spans="2:22" ht="66" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
@@ -5781,11 +5780,11 @@
       <c r="S7" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="T7" s="130"/>
-      <c r="U7" s="136" t="s">
+      <c r="T7" s="119"/>
+      <c r="U7" s="125" t="s">
         <v>59</v>
       </c>
-      <c r="V7" s="137"/>
+      <c r="V7" s="126"/>
     </row>
     <row r="8" spans="2:22" ht="66" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="8" t="s">
@@ -5812,14 +5811,14 @@
       <c r="S8" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="T8" s="129"/>
-      <c r="U8" s="134" t="s">
+      <c r="T8" s="118"/>
+      <c r="U8" s="123" t="s">
         <v>58</v>
       </c>
-      <c r="V8" s="135"/>
+      <c r="V8" s="124"/>
     </row>
     <row r="9" spans="2:22" ht="66" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="99" t="s">
+      <c r="B9" s="159" t="s">
         <v>65</v>
       </c>
       <c r="C9" s="15" t="s">
@@ -5857,12 +5856,12 @@
       <c r="S9" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="T9" s="131"/>
-      <c r="U9" s="133"/>
+      <c r="T9" s="120"/>
+      <c r="U9" s="122"/>
       <c r="V9" s="96"/>
     </row>
     <row r="10" spans="2:22" ht="66" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="100"/>
+      <c r="B10" s="160"/>
       <c r="C10" s="23" t="s">
         <v>9</v>
       </c>
@@ -5877,10 +5876,10 @@
         <v>68</v>
       </c>
       <c r="J10" s="10"/>
-      <c r="K10" s="108" t="s">
+      <c r="K10" s="157" t="s">
         <v>102</v>
       </c>
-      <c r="L10" s="109"/>
+      <c r="L10" s="158"/>
       <c r="M10" s="13" t="s">
         <v>74</v>
       </c>
@@ -5896,12 +5895,12 @@
       <c r="S10" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="T10" s="128"/>
-      <c r="U10" s="133"/>
+      <c r="T10" s="117"/>
+      <c r="U10" s="122"/>
       <c r="V10" s="96"/>
     </row>
     <row r="11" spans="2:22" ht="66" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="100"/>
+      <c r="B11" s="160"/>
       <c r="C11" s="18" t="s">
         <v>85</v>
       </c>
@@ -5935,12 +5934,12 @@
       </c>
       <c r="R11" s="81"/>
       <c r="S11" s="87"/>
-      <c r="T11" s="128"/>
-      <c r="U11" s="133"/>
+      <c r="T11" s="117"/>
+      <c r="U11" s="122"/>
       <c r="V11" s="96"/>
     </row>
     <row r="12" spans="2:22" ht="66" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="100"/>
+      <c r="B12" s="160"/>
       <c r="C12" s="23" t="s">
         <v>60</v>
       </c>
@@ -5974,12 +5973,12 @@
       </c>
       <c r="R12" s="81"/>
       <c r="S12" s="87"/>
-      <c r="T12" s="128"/>
-      <c r="U12" s="133"/>
+      <c r="T12" s="117"/>
+      <c r="U12" s="122"/>
       <c r="V12" s="96"/>
     </row>
     <row r="13" spans="2:22" ht="66" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="100"/>
+      <c r="B13" s="160"/>
       <c r="C13" s="23"/>
       <c r="D13" s="22"/>
       <c r="E13" s="33"/>
@@ -6003,12 +6002,12 @@
       </c>
       <c r="R13" s="81"/>
       <c r="S13" s="87"/>
-      <c r="T13" s="128"/>
-      <c r="U13" s="133"/>
+      <c r="T13" s="117"/>
+      <c r="U13" s="122"/>
       <c r="V13" s="96"/>
     </row>
     <row r="14" spans="2:22" ht="66" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="100"/>
+      <c r="B14" s="160"/>
       <c r="C14" s="24"/>
       <c r="D14" s="20"/>
       <c r="E14" s="33"/>
@@ -6032,12 +6031,12 @@
       </c>
       <c r="R14" s="81"/>
       <c r="S14" s="87"/>
-      <c r="T14" s="128"/>
-      <c r="U14" s="133"/>
+      <c r="T14" s="117"/>
+      <c r="U14" s="122"/>
       <c r="V14" s="96"/>
     </row>
     <row r="15" spans="2:22" ht="66" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="100"/>
+      <c r="B15" s="160"/>
       <c r="C15" s="23"/>
       <c r="D15" s="22"/>
       <c r="E15" s="33"/>
@@ -6059,12 +6058,12 @@
       </c>
       <c r="R15" s="81"/>
       <c r="S15" s="87"/>
-      <c r="T15" s="128"/>
-      <c r="U15" s="133"/>
+      <c r="T15" s="117"/>
+      <c r="U15" s="122"/>
       <c r="V15" s="96"/>
     </row>
     <row r="16" spans="2:22" ht="66" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="100"/>
+      <c r="B16" s="160"/>
       <c r="C16" s="23"/>
       <c r="D16" s="22"/>
       <c r="E16" s="33"/>
@@ -6084,35 +6083,35 @@
       </c>
       <c r="R16" s="81"/>
       <c r="S16" s="87"/>
-      <c r="T16" s="128"/>
-      <c r="U16" s="133"/>
+      <c r="T16" s="117"/>
+      <c r="U16" s="122"/>
       <c r="V16" s="96"/>
     </row>
     <row r="17" spans="2:22" ht="66" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="101"/>
-      <c r="C17" s="110"/>
-      <c r="D17" s="111"/>
-      <c r="E17" s="112"/>
-      <c r="F17" s="113"/>
-      <c r="G17" s="114"/>
-      <c r="H17" s="115"/>
-      <c r="I17" s="116"/>
-      <c r="J17" s="117"/>
-      <c r="K17" s="118"/>
-      <c r="L17" s="119"/>
-      <c r="M17" s="120"/>
-      <c r="N17" s="121"/>
-      <c r="O17" s="122"/>
-      <c r="P17" s="123"/>
-      <c r="Q17" s="124"/>
-      <c r="R17" s="125"/>
-      <c r="S17" s="126"/>
-      <c r="T17" s="132"/>
-      <c r="U17" s="138"/>
-      <c r="V17" s="139"/>
+      <c r="B17" s="161"/>
+      <c r="C17" s="99"/>
+      <c r="D17" s="100"/>
+      <c r="E17" s="101"/>
+      <c r="F17" s="102"/>
+      <c r="G17" s="103"/>
+      <c r="H17" s="104"/>
+      <c r="I17" s="105"/>
+      <c r="J17" s="106"/>
+      <c r="K17" s="107"/>
+      <c r="L17" s="108"/>
+      <c r="M17" s="109"/>
+      <c r="N17" s="110"/>
+      <c r="O17" s="111"/>
+      <c r="P17" s="112"/>
+      <c r="Q17" s="113"/>
+      <c r="R17" s="114"/>
+      <c r="S17" s="115"/>
+      <c r="T17" s="121"/>
+      <c r="U17" s="127"/>
+      <c r="V17" s="128"/>
     </row>
     <row r="18" spans="2:22" ht="66" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="102" t="s">
+      <c r="B18" s="148" t="s">
         <v>66</v>
       </c>
       <c r="C18" s="25" t="s">
@@ -6143,7 +6142,7 @@
       <c r="V18" s="95"/>
     </row>
     <row r="19" spans="2:22" ht="66" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="103"/>
+      <c r="B19" s="149"/>
       <c r="C19" s="27"/>
       <c r="D19" s="22"/>
       <c r="E19" s="33"/>
@@ -6168,7 +6167,7 @@
       <c r="V19" s="96"/>
     </row>
     <row r="20" spans="2:22" ht="66" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="103"/>
+      <c r="B20" s="149"/>
       <c r="C20" s="27"/>
       <c r="D20" s="22"/>
       <c r="E20" s="33"/>
@@ -6191,7 +6190,7 @@
       <c r="V20" s="96"/>
     </row>
     <row r="21" spans="2:22" ht="66" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="103"/>
+      <c r="B21" s="149"/>
       <c r="C21" s="27"/>
       <c r="D21" s="22"/>
       <c r="E21" s="33"/>
@@ -6214,7 +6213,7 @@
       <c r="V21" s="96"/>
     </row>
     <row r="22" spans="2:22" ht="66" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="103"/>
+      <c r="B22" s="149"/>
       <c r="C22" s="27"/>
       <c r="D22" s="22"/>
       <c r="E22" s="33"/>
@@ -6237,7 +6236,7 @@
       <c r="V22" s="96"/>
     </row>
     <row r="23" spans="2:22" ht="66" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="104"/>
+      <c r="B23" s="150"/>
       <c r="C23" s="28"/>
       <c r="D23" s="29"/>
       <c r="E23" s="36"/>
@@ -6279,6 +6278,12 @@
     <row r="41" ht="66" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B18:B23"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="B9:B17"/>
     <mergeCell ref="U2:V2"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="K2:L2"/>
@@ -6287,12 +6292,6 @@
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="I2:J2"/>
-    <mergeCell ref="B18:B23"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="B9:B17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
